--- a/esyluban/examples/dev/DataTables/test/test_desc.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_desc.xlsx
@@ -529,6 +529,16 @@
           <t>x2:byte</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>x3:short</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>x4:int</t>
+        </is>
+      </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
           <t>这是x2</t>
@@ -537,6 +547,11 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>x5:long</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>x6:float</t>
         </is>
       </c>
     </row>
@@ -678,6 +693,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="B8" t="n">
         <v>1</v>
@@ -725,12 +741,12 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I4:J4"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="K4:L4"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I1:J1"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="I3:J3"/>
   </mergeCells>
